--- a/data/reviewing.xlsx
+++ b/data/reviewing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conorisco/Dropbox (Personal)/Jobs/CV and Publications/CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE9BCD0-4BE4-4B4B-B38E-3F2538F1910C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D987EE-A462-ED41-9460-CA48C2461513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1760" yWindow="2280" windowWidth="28160" windowHeight="22380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t>with</t>
   </si>
@@ -153,6 +153,15 @@
   </si>
   <si>
     <t>2023-2025</t>
+  </si>
+  <si>
+    <t>Kidney Research UK Clinical fellowships</t>
+  </si>
+  <si>
+    <t>Kidney Research UK project grants</t>
+  </si>
+  <si>
+    <t>PhD studentship (Redacted UK Cancer Charity)</t>
   </si>
 </sst>
 </file>
@@ -514,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -770,6 +779,39 @@
         <v>38</v>
       </c>
     </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25">
+        <v>2025</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/reviewing.xlsx
+++ b/data/reviewing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conorisco/Dropbox (Personal)/Jobs/CV and Publications/CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D987EE-A462-ED41-9460-CA48C2461513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00BE4C4-D113-CC47-927C-71196BE8B40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="2280" windowWidth="28160" windowHeight="22380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1760" yWindow="660" windowWidth="28160" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
   <si>
     <t>with</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>PhD studentship (Redacted UK Cancer Charity)</t>
+  </si>
+  <si>
+    <t>Immuity &amp; Aging</t>
   </si>
 </sst>
 </file>
@@ -523,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -812,6 +815,17 @@
         <v>2025</v>
       </c>
     </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
